--- a/product_surveys/028_energy_drink_consumption_survey--product_surveys.xlsx
+++ b/product_surveys/028_energy_drink_consumption_survey--product_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,8 +442,8 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,33 +525,37 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Energy Drink Consumption Survey</t>
+          <t>Energy Drink Consumption</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>perceived_health_risks</t>
+          <t>consumption_frequency_other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>perceived_health_risks</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>If other, please specify the frequency</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -561,23 +565,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>consumption_frequency</t>
+          <t>reasons_for_consumption</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>consumption_frequency</t>
+          <t>Reasons for Consumption</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,15 +593,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>consumption_frequency_other</t>
+          <t>reasons_for_consumption_other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>if_other</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Reasons For Consumption Other</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>If other, please specify your reason</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -612,18 +620,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>reasons_for_consumption</t>
+          <t>side_effects</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>reasons_for_consumption</t>
+          <t>Side Effects</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,15 +643,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>reasons_for_consumption_other</t>
+          <t>side_effects_other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>if_other</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Side Effects Other</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>If other, please specify the side effect</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -658,18 +670,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>side_effects</t>
+          <t>consumption_amount</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>side_effects</t>
+          <t>Consumption Amount</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,15 +693,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>side_effects_other</t>
+          <t>consumption_amount_other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>if_other</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Consumption Amount Other</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>If other, please specify the amount</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -699,23 +715,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>consumption_amount</t>
+          <t>duration_of_consumption</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>consumption_amount</t>
+          <t>Duration of Consumption</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,12 +743,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>consumption_amount_other</t>
+          <t>daily_routine</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>if_other</t>
+          <t>Daily Routine</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -753,7 +769,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
@@ -786,12 +802,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>energy_drink_not_consumed</t>
+          <t>never_consumed</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Energy drink not consumed</t>
+          <t>Never Consumed</t>
         </is>
       </c>
     </row>
@@ -803,12 +819,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>consumed_1-2_times_a_month</t>
+          <t>less_than_once_a_month</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Consumed 1-2 times a month</t>
+          <t>Less than once a month</t>
         </is>
       </c>
     </row>
@@ -820,12 +836,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>consumed_3-4_times_a_month</t>
+          <t>1-2_times_a_month</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Consumed 3-4 times a month</t>
+          <t>1-2 times a month</t>
         </is>
       </c>
     </row>
@@ -837,12 +853,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>consumed_5-6_times_a_month</t>
+          <t>3-4_times_a_month</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Consumed 5-6 times a month</t>
+          <t>3-4 times a month</t>
         </is>
       </c>
     </row>
@@ -854,138 +870,138 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>consumed_every_day</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Consumed every day</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>energy_drink_consumption_survey_choices</t>
+          <t>reasons_for_consumption_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>consumed_daily</t>
+          <t>energy_and_alertness</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Consumed daily</t>
+          <t>Energy and alertness</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>perceived_health_risks_choices</t>
+          <t>reasons_for_consumption_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>taste</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Taste</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>perceived_health_risks_choices</t>
+          <t>reasons_for_consumption_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>headaches</t>
+          <t>social_events</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Headaches</t>
+          <t>Social events</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>perceived_health_risks_choices</t>
+          <t>reasons_for_consumption_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>insomnia</t>
+          <t>to_relax_or_relieve_stress</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Insomnia</t>
+          <t>To relax or relieve stress</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>perceived_health_risks_choices</t>
+          <t>side_effects_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>anxiety</t>
+          <t>headaches</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Anxiety</t>
+          <t>Headaches</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>perceived_health_risks_choices</t>
+          <t>side_effects_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>depression</t>
+          <t>insomnia</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Depression</t>
+          <t>Insomnia</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>perceived_health_risks_choices</t>
+          <t>side_effects_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>heart_issues</t>
+          <t>anxiety</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Heart issues</t>
+          <t>Anxiety</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>perceived_health_risks_choices</t>
+          <t>side_effects_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1002,457 +1018,83 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>perceived_health_risks_choices</t>
+          <t>consumption_amount_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>less_than_500ml</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Less than 500ml</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>perceived_health_risks_choices</t>
+          <t>consumption_amount_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>specify</t>
+          <t>500ml-1000ml</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Specify</t>
+          <t>500ml-1000ml</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>consumption_frequency_choices</t>
+          <t>consumption_amount_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>1-2l</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1-2L</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>consumption_frequency_choices</t>
+          <t>consumption_amount_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1-3_times_a_year</t>
+          <t>2-4l</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1-3 times a year</t>
+          <t>2-4L</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>consumption_frequency_choices</t>
+          <t>consumption_amount_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1-3_times_a_month</t>
+          <t>4l_or_more</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
-        <is>
-          <t>1-3 times a month</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>consumption_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1-3_times_a_week</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>1-3 times a week</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>consumption_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>consumption_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>weekly_or_more</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Weekly or more</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>reasons_for_consumption_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>energy_and_alertness</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Energy and alertness</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>reasons_for_consumption_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>taste</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Taste</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>reasons_for_consumption_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>social_events</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Social events</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>reasons_for_consumption_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>to_relax_or_relieve_stress</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>To relax or relieve stress</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>reasons_for_consumption_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>reasons_for_consumption_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>specify</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Specify</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>side_effects_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>side_effects_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>headaches</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Headaches</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>side_effects_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>insomnia</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Insomnia</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>side_effects_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>anxiety</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Anxiety</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>side_effects_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>depression</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Depression</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>side_effects_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>high_blood_pressure</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>High blood pressure</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>side_effects_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>side_effects_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>specify</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Specify</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>consumption_amount_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>less_than_500ml</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Less than 500ml</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>consumption_amount_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>500ml-1000ml</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>500ml-1000ml</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>consumption_amount_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>1-2l</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>1-2L</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>consumption_amount_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2-4l</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>2-4L</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>consumption_amount_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>4l_or_more</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
         <is>
           <t>4L or more</t>
         </is>
